--- a/AAII_Financials/Quarterly/BKNIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKNIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="92">
   <si>
     <t>BKNIY</t>
   </si>
@@ -656,95 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -787,32 +790,35 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3">
         <v>1105800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>492300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>837000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>400100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>791100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>388300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>758300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>371100</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -879,8 +885,11 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +956,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,8 +985,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1041,8 +1054,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1109,8 +1125,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1153,8 +1172,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1177,8 +1196,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1221,32 +1243,35 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3">
         <v>-44500</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>-43400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-21500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-42800</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>-40600</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1268,8 +1293,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1312,32 +1338,35 @@
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>302200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>131300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>229600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>108000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>247900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>113100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>217600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>103300</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1380,32 +1409,35 @@
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>803600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>360900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>607400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>292100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>543200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>275300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>540700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>267800</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1430,8 +1462,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1474,32 +1507,35 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-348200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-114900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-59600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-273100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-108100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-236400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1542,32 +1578,35 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>544100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>450200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>354400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>344800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1610,8 +1649,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1634,8 +1673,11 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1678,32 +1720,35 @@
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>455400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>246100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>406800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>232500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>270100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>167100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>304300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>169900</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1746,32 +1791,35 @@
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>135100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>74100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>111900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>65100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>61000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>48200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>87800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1838,8 +1886,11 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1882,32 +1933,35 @@
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>320300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>172000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>294900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>167400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>209100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>118900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>216400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>123100</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1950,32 +2004,35 @@
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>320300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>172000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>294900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>167400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>209100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>118900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>216400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>123100</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2042,8 +2099,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2086,8 +2146,8 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2105,13 +2165,16 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>989900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2178,8 +2241,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2246,8 +2312,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2290,32 +2359,35 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>348200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>114900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>59600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>273100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>108100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>236400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>97900</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2358,32 +2430,35 @@
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>320300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>172000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>294900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>167400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>209100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>118900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1206400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>156900</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2450,8 +2525,11 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2494,105 +2572,111 @@
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>320300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>172000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>294900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>167400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>209100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>118900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1206400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>156900</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2617,8 +2701,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2643,189 +2728,196 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14575000</v>
+      </c>
+      <c r="E41" s="3">
         <v>13278100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4719700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15849400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15409600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12499300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5167500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14384800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12195700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10660700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1709700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13243400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13357300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14304500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>18950800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22304600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26421000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>28526100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>26864400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>23799900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22566900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20652800</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7848800</v>
+      </c>
+      <c r="E42" s="3">
         <v>7751400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5782100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7582800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7575300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5559000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4034200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8083700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6928400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5521700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5505500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4823800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4887700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4756200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>15561500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>17275800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14263600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13690100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>12989400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>12401900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>12497500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>13266800</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>482000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1009600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>614300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>744400</v>
       </c>
-      <c r="G43" s="3">
-        <v>517400</v>
-      </c>
       <c r="H43" s="3">
+        <v>1121900</v>
+      </c>
+      <c r="I43" s="3">
         <v>987700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>559300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>704100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>982200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>864100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>518500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>577100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>303300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>712200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -2847,25 +2939,28 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3">
         <v>16000</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>5</v>
+      <c r="H44" s="3">
+        <v>21400</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>5</v>
@@ -2873,26 +2968,26 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>26300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="3">
         <v>41600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>46000</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2915,53 +3010,56 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>149700</v>
+      </c>
+      <c r="E45" s="3">
         <v>151900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>446200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>170100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>178800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>174100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>436200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>193100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>186200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>194700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>495400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>203800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>169100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>234000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -2983,53 +3081,56 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23055500</v>
+      </c>
+      <c r="E46" s="3">
         <v>22207000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24454900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24346600</v>
       </c>
-      <c r="G46" s="3">
-        <v>23681100</v>
-      </c>
       <c r="H46" s="3">
+        <v>24307000</v>
+      </c>
+      <c r="I46" s="3">
         <v>19220000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20991900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23365700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20318800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17241100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21839000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18889700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18763500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20006900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3051,212 +3152,224 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>136433600</v>
+      </c>
+      <c r="E47" s="3">
         <v>19817800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19439300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>19461000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19326000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16947700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>16223900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>16008600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>15281000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13816500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13511600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12936200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12947300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12802700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>197400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>201300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>199600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>194300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>184300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>186300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>170300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>120900</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>536100</v>
+      </c>
+      <c r="E48" s="3">
         <v>540000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>545700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>535000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>524100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>482300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>457900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>479800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>461800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>461100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>468900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>462000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>478400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>479700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>496000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>481900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>485800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>481400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>488300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>487100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>485600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>485400</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>429300</v>
+      </c>
+      <c r="E49" s="3">
         <v>422800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>435500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>408900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>380200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>343400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>331800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>349300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>329300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>323700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>333800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>300400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>307400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>301200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>309000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>291200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>292800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>289100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>292400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>284000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>280200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>275700</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3323,8 +3436,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3391,76 +3507,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>230300</v>
       </c>
       <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
         <v>75900</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
-        <v>294500</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>59300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>54000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>199200</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>584600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>89800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>378200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>107400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>411900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>127100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>415100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1858000</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3527,76 +3649,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>161011200</v>
+      </c>
+      <c r="E54" s="3">
         <v>157590300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>153832200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>151005600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>154707700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>133864300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>126277900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>132027200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>126861500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>121845100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>124916200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>114693700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>120195800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>115108400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119074800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>119416000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>121311900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120219300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>116631900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>110348400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>108598700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>106669300</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3621,8 +3749,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3647,53 +3776,54 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>131598000</v>
+      </c>
+      <c r="E57" s="3">
         <v>130547300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>109980700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>123261100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>125133900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>110176200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>92945900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>104455900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>102029300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>98309500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>101987400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>91285700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>96822800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>93703700</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -3715,53 +3845,56 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1038100</v>
+      </c>
+      <c r="E58" s="3">
         <v>232500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17494400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>299800</v>
       </c>
-      <c r="G58" s="3">
-        <v>1527200</v>
-      </c>
       <c r="H58" s="3">
+        <v>263300</v>
+      </c>
+      <c r="I58" s="3">
         <v>284700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13147500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>503500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>396600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>505700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1556100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>438200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1471300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>446000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -3783,121 +3916,127 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1718900</v>
+      </c>
+      <c r="E59" s="3">
         <v>3318300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3152800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3770300</v>
       </c>
-      <c r="G59" s="3">
-        <v>2096800</v>
-      </c>
       <c r="H59" s="3">
+        <v>3841800</v>
+      </c>
+      <c r="I59" s="3">
         <v>3037900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2376200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6513100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6182500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5510200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3854200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4510400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2572800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3767500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>256900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>565400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>226400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>498300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>150700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>637400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>178100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>458800</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>134355100</v>
+      </c>
+      <c r="E60" s="3">
         <v>134098100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>131095900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>127331300</v>
       </c>
-      <c r="G60" s="3">
-        <v>128757900</v>
-      </c>
       <c r="H60" s="3">
+        <v>129238900</v>
+      </c>
+      <c r="I60" s="3">
         <v>113498900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>109027600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>111472500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>108608500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>104325500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>108062900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>96234300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100866800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>97917200</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -3919,144 +4058,153 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12620200</v>
+      </c>
+      <c r="E61" s="3">
         <v>11508100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12313500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11808800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11939700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10030100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9389100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10066900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8557300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8667100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9556300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8940500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8361300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7507000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7125300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6275600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7595700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8130400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8336600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8525400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8574600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7982000</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6274900</v>
+      </c>
+      <c r="E62" s="3">
         <v>4482600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2785000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4303200</v>
       </c>
-      <c r="G62" s="3">
-        <v>6607200</v>
-      </c>
       <c r="H62" s="3">
+        <v>6234500</v>
+      </c>
+      <c r="I62" s="3">
         <v>3799900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1687200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3884200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3648600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2991300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1341900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3917100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5340300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4274300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>482200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>405100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>469300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>425300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>580400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>472100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>554000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1496900</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4123,8 +4271,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4191,8 +4342,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4259,76 +4413,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>153353100</v>
+      </c>
+      <c r="E66" s="3">
         <v>150088800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>146304300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>143443200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>147413100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>127328900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>120192700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>125423500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>120814300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>115983900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>119032500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>109092000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>114630900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>109698600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>113642000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>114134600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>116073400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>114951000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>111371700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>105127800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>103437200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>101326400</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4353,8 +4513,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4421,8 +4582,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4489,8 +4653,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4557,8 +4724,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4625,76 +4795,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>7380400</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>7259700</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="3">
-        <v>6941600</v>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>5839100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>5714100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>5450000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>5265300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>5011800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>4837100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>4700800</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4761,8 +4937,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4829,8 +5008,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4897,76 +5079,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7658100</v>
+      </c>
+      <c r="E76" s="3">
         <v>7501600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7527900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7562400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7294700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6535400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6085200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6603700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6047200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5861300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5883700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5601800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5565000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5409900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5432700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5281400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5238500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5268300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5260200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5220600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5161500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5342900</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5033,81 +5221,87 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5150,32 +5344,35 @@
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>320300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>172000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>294900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>167400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>209100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>118900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1206400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>156900</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5200,8 +5397,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5244,32 +5442,35 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>88700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>43400</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>84300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>40600</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5336,8 +5537,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5404,8 +5608,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5472,8 +5679,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5540,8 +5750,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5608,8 +5821,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5652,32 +5868,35 @@
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>-8899500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>-1242900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>7643800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>3453400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5702,8 +5921,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5746,8 +5966,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5765,13 +5985,16 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-8400</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5838,8 +6061,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5906,8 +6132,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5950,32 +6179,35 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-259200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-19100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-69300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-62600</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6000,8 +6232,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6044,32 +6277,35 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-279600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-129800</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-228500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-47300</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6136,8 +6372,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6204,8 +6443,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6272,8 +6514,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6316,32 +6561,35 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-833900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-674200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>370600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>536700</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6384,8 +6632,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6408,8 +6656,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6452,28 +6703,31 @@
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>-9992600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1936100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>7945100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>3927500</v>
       </c>
-      <c r="X102" s="3" t="s">
+      <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
